--- a/Doc/玛法放置 - 01.xlsx
+++ b/Doc/玛法放置 - 01.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375" tabRatio="759"/>
+    <workbookView windowHeight="17680" tabRatio="759"/>
   </bookViews>
   <sheets>
     <sheet name="总体思路" sheetId="19" r:id="rId1"/>
@@ -27,132 +27,27 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>游戏内容</t>
   </si>
   <si>
-    <t>整体思路</t>
+    <t>1，主线地图（击杀通关boss，就可以解锁下一个地图，设计通关boss难度，前期可以卡住玩家，后期新人也可以快速追上）</t>
   </si>
   <si>
-    <t>开发一个月</t>
+    <t>2，boss之家，每天4-6次，看广告恢复4次，挑战模式为，所有通过关卡的boss，轮流出现</t>
   </si>
   <si>
-    <t>玩家只玩一个月，通过</t>
+    <t>3。挖矿（洞府功能），击杀boss掉落材料解锁，矿洞可以挖掘金币和秘矿，秘矿精炼装备</t>
   </si>
   <si>
-    <t>无尽塔</t>
+    <t>4，通天塔，一次性玩法，奖励大量资源</t>
   </si>
   <si>
-    <t>奖励</t>
+    <t>5，付费功能，参照KK，付费道具放在服务器，没人每天给10次服务器抽奖功能，抽取付费道具或者积分，积分可以兑换付费道具，规避破解功能</t>
   </si>
   <si>
-    <t>道具，金币，称号 等</t>
-  </si>
-  <si>
-    <t>玩法</t>
-  </si>
-  <si>
-    <t>每层都是boss，特殊层数会给boss手动设定技能，地形，因此是唯一需要过图动脑的地方</t>
-  </si>
-  <si>
-    <t>地图</t>
-  </si>
-  <si>
-    <t>装备来源</t>
-  </si>
-  <si>
-    <t>部分经验来源</t>
-  </si>
-  <si>
-    <t>离线需要看广告，广告来源</t>
-  </si>
-  <si>
-    <t>BOSS，累积制，把下线累积的boss，累积起来，上限5只</t>
-  </si>
-  <si>
-    <t>开图限制，等级，防止版本更新，一次打穿</t>
-  </si>
-  <si>
-    <t>技能</t>
-  </si>
-  <si>
-    <t>人物技能：只有一个技能-招魂（默认为雷电，换个颜色），击杀怪物，有概率让怪物直接变成自己的宠物，并且按属性获得一定的提升</t>
-  </si>
-  <si>
-    <t>宠物技能：采用龙城1的技能</t>
-  </si>
-  <si>
-    <t>属性</t>
-  </si>
-  <si>
-    <t>分3种，武力，道力，法力</t>
-  </si>
-  <si>
-    <t>升级增加，各种培养系统都增加</t>
-  </si>
-  <si>
-    <t>图鉴，同时加3职业属性，给跨职业玩法提供可能性</t>
-  </si>
-  <si>
-    <t>装备</t>
-  </si>
-  <si>
-    <t>全部随机技能，无限搭配，任意组合</t>
-  </si>
-  <si>
-    <t>分三系，战力系 加武力+战士技能，法师系，加法力+法师技能，道士系 道力+道士技能</t>
-  </si>
-  <si>
-    <t>名称从传奇取，用完了就轮回用</t>
-  </si>
-  <si>
-    <t>图鉴</t>
-  </si>
-  <si>
-    <t>为了不让各种地图无效，增加图鉴掉落，运气不好，只有刷够才能掉落，控制时间范围，中期图鉴控制0.5-1天全部掉落</t>
-  </si>
-  <si>
-    <t>其他属性系统</t>
-  </si>
-  <si>
-    <t>翅膀，坐骑，宠物，统统搞起来</t>
-  </si>
-  <si>
-    <t>其他玩法</t>
-  </si>
-  <si>
-    <t>活动</t>
-  </si>
-  <si>
-    <t>单机游戏，可以预制节日双倍经验爆率等，节日物品爆率</t>
-  </si>
-  <si>
-    <t>在线时间</t>
-  </si>
-  <si>
-    <t>清理boss，爬塔，调整装备属性等</t>
-  </si>
-  <si>
-    <t>难点</t>
-  </si>
-  <si>
-    <t>数值合理性</t>
-  </si>
-  <si>
-    <t>召唤物ai</t>
-  </si>
-  <si>
-    <t>解决方案</t>
-  </si>
-  <si>
-    <t>存档加密</t>
-  </si>
-  <si>
-    <t>首次进游戏联网百度取个时间戳</t>
-  </si>
-  <si>
-    <t>检测修改者，关闭游戏</t>
+    <t>6，暂定词条，专属，图鉴</t>
   </si>
 </sst>
 </file>
@@ -187,6 +82,14 @@
     </font>
     <font>
       <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="9"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
@@ -211,14 +114,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="16"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -363,7 +258,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -379,6 +274,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -693,7 +594,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -717,16 +618,16 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -735,95 +636,97 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1146,8 +1049,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J59"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <dimension ref="A1:T60"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
     <col min="2" max="2" width="10.625" style="1" customWidth="1"/>
@@ -1155,242 +1058,113 @@
     <col min="4" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="20.25" spans="3:10">
-      <c r="C1" s="3"/>
-      <c r="J1" s="8" t="s">
+    <row r="1" s="1" customFormat="1" ht="20" spans="1:10">
+      <c r="C1" s="4"/>
+      <c r="J1" s="5" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" s="2" customFormat="1" spans="1:1">
-      <c r="A3" s="4" t="s">
+    <row r="3" s="2" customFormat="1"/>
+    <row r="5" customFormat="1" ht="14"/>
+    <row r="6" s="3" customFormat="1" ht="13.5" spans="1:10">
+      <c r="A6" s="6" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" spans="2:3">
-      <c r="B4" s="1" t="s">
+    <row r="11" s="2" customFormat="1" ht="13.5" spans="1:10">
+      <c r="A11" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="1" t="s">
+    </row>
+    <row r="13" s="1" customFormat="1" spans="1:10">
+      <c r="B13" s="8"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+    </row>
+    <row r="14" s="1" customFormat="1" spans="1:10">
+      <c r="B14" s="8"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="9"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+    </row>
+    <row r="15" s="1" customFormat="1" spans="1:10">
+      <c r="B15" s="8"/>
+    </row>
+    <row r="16" s="1" customFormat="1" spans="1:10">
+      <c r="B16" s="8"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+    </row>
+    <row r="17" s="2" customFormat="1" ht="13.5" spans="1:4">
+      <c r="A17" s="7" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" customFormat="1" spans="1:1">
-      <c r="A5" s="1"/>
-    </row>
-    <row r="6" s="2" customFormat="1" spans="1:1">
-      <c r="A6" s="4" t="s">
+    <row r="22" s="2" customFormat="1" ht="13.5" spans="1:4">
+      <c r="A22" s="7" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" spans="2:3">
-      <c r="B7" s="1" t="s">
+    <row r="27" s="2" customFormat="1" ht="13.5" spans="1:4">
+      <c r="A27" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="1" t="s">
+    </row>
+    <row r="28" s="1" customFormat="1" spans="1:4">
+      <c r="D28" s="10"/>
+    </row>
+    <row r="32" s="2" customFormat="1" ht="13.5" spans="1:4">
+      <c r="A32" s="7" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" spans="2:3">
-      <c r="B8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" s="2" customFormat="1" spans="1:1">
-      <c r="A11" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" spans="3:3">
-      <c r="C12" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" s="1" customFormat="1" spans="2:9">
-      <c r="B13" s="5"/>
-      <c r="C13" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
-    </row>
-    <row r="14" s="1" customFormat="1" spans="2:9">
-      <c r="B14" s="5"/>
-      <c r="C14" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
-    </row>
-    <row r="15" s="1" customFormat="1" spans="2:3">
-      <c r="B15" s="5"/>
-      <c r="C15" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" s="1" customFormat="1" spans="2:9">
-      <c r="B16" s="5"/>
-      <c r="C16" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="5"/>
-      <c r="I16" s="5"/>
-    </row>
-    <row r="17" s="2" customFormat="1" spans="1:1">
-      <c r="A17" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="18" s="1" customFormat="1" spans="2:2">
-      <c r="B18" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="19" s="1" customFormat="1" spans="2:2">
-      <c r="B19" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="22" s="2" customFormat="1" spans="1:1">
-      <c r="A22" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="23" s="1" customFormat="1" spans="2:2">
-      <c r="B23" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="24" s="1" customFormat="1" spans="2:2">
-      <c r="B24" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="25" s="1" customFormat="1" spans="2:2">
-      <c r="B25" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="27" s="2" customFormat="1" spans="1:1">
-      <c r="A27" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="28" s="1" customFormat="1" spans="2:4">
-      <c r="B28" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D28" s="7"/>
-    </row>
-    <row r="29" s="1" customFormat="1" spans="2:2">
-      <c r="B29" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="30" s="1" customFormat="1" spans="2:2">
-      <c r="B30" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="32" s="2" customFormat="1" spans="1:1">
-      <c r="A32" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="33" spans="2:8">
-      <c r="B33" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="6"/>
-      <c r="G33" s="5"/>
-      <c r="H33" s="5"/>
-    </row>
-    <row r="37" s="2" customFormat="1" spans="1:1">
-      <c r="A37" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="38" spans="2:2">
-      <c r="B38" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="41" s="2" customFormat="1" spans="1:1">
-      <c r="A41" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="45" s="2" customFormat="1" spans="1:1">
-      <c r="A45" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="46" spans="2:2">
-      <c r="B46" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="48" s="2" customFormat="1" spans="1:1">
-      <c r="A48" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="49" s="2" customFormat="1" spans="1:2">
-      <c r="A49" s="4"/>
-      <c r="B49" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="51" s="2" customFormat="1" spans="1:1">
-      <c r="A51" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="52" spans="2:2">
-      <c r="B52" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="53" spans="2:2">
-      <c r="B53" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="56" s="2" customFormat="1" spans="1:1">
-      <c r="A56" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="57" spans="2:2">
-      <c r="B57" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="58" spans="2:2">
-      <c r="B58" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="59" spans="2:2">
-      <c r="B59" s="1" t="s">
-        <v>41</v>
+    <row r="33" spans="1:8">
+      <c r="B33" s="9"/>
+      <c r="C33" s="9"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="9"/>
+      <c r="F33" s="9"/>
+      <c r="G33" s="8"/>
+      <c r="H33" s="8"/>
+    </row>
+    <row r="37" s="2" customFormat="1" ht="13.5" spans="1:8">
+      <c r="A37" s="7"/>
+    </row>
+    <row r="41" s="2" customFormat="1" ht="13.5" spans="1:8">
+      <c r="A41" s="7"/>
+    </row>
+    <row r="45" s="2" customFormat="1" ht="13.5" spans="1:8">
+      <c r="A45" s="7"/>
+    </row>
+    <row r="48" s="2" customFormat="1" ht="13.5" spans="1:8">
+      <c r="A48" s="7"/>
+    </row>
+    <row r="49" s="2" customFormat="1" ht="13.5" spans="1:20">
+      <c r="A49" s="7"/>
+    </row>
+    <row r="51" s="2" customFormat="1" ht="13.5" spans="1:20">
+      <c r="A51" s="7"/>
+    </row>
+    <row r="56" s="2" customFormat="1" ht="13.5" spans="1:20">
+      <c r="A56" s="7"/>
+    </row>
+    <row r="60" spans="1:20">
+      <c r="T60" s="1">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
